--- a/frontend/public/sablon/muadil-veri-sablonu.xlsx
+++ b/frontend/public/sablon/muadil-veri-sablonu.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parfümler" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Muadiller" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nasıl doldurulur" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Parfümler" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Muadiller" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Nasıl doldurulur" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E501"/>
+  <dimension ref="A1:F501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -476,6 +476,7 @@
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -504,6 +505,11 @@
           <t>Alt notalar</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Cinsiyet</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -4006,6 +4012,11 @@
       <c r="E501" s="2" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Cinsiyet" error="Kadın, Erkek, Unisex seç ya da boş bırak (Unisex sayılır)." type="list">
+      <formula1>"Kadın,Erkek,Unisex"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4016,7 +4027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H501"/>
+  <dimension ref="A1:I501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4027,6 +4038,7 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4070,6 +4082,11 @@
           <t>Ürün linki</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cinsiyet</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -9072,7 +9089,7 @@
       <c r="H501" s="2" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="E2:E501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Fiyat" error="1 ile 100000 arasında bir sayı gir." type="decimal" operator="between">
       <formula1>1</formula1>
       <formula2>100000</formula2>
@@ -9080,6 +9097,9 @@
     <dataValidation sqref="F2:G501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Puan" error="1 ile 10 arasında bir tam sayı gir." type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>10</formula2>
+    </dataValidation>
+    <dataValidation sqref="I2:I501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Cinsiyet" error="Kadın, Erkek, Unisex seç ya da boş bırak (Unisex sayılır)." type="list">
+      <formula1>"Kadın,Erkek,Unisex"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9092,7 +9112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9144,174 +9164,204 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cinsiyet sütunu boş bırakılırsa Unisex sayılır. Yalnız bir marka aynı kodu kadın ve erkek üründe ayrı ayrı kullanıyorsa (ör. Mad A114) doldur; aksi halde boş geç.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Sistemde olmayan markalar ve notalar otomatik oluşturulur; yüklemeden önce kontrol ekranında listelenir.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Aynı dosyayı tekrar yüklersen çift kayıt oluşmaz: aynı marka + parfüm güncellenir, aynı muadil marka + kod güncellenir.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Bir satırda bile hata varsa hiçbir şey kaydedilmez; hatalar sayfa ve satır numarasıyla gösterilir.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Örnek: Parfümler sayfasında bir satır</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Marka</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Parfüm</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Üst notalar</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>Orta notalar</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Alt notalar</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Cinsiyet</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Dior</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Sauvage</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Bergamot, Biber</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Lavanta, Pembe biber</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Ambroksan, Sedir</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Örnek: Muadiller sayfasında bir satır</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Orijinal marka</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Parfüm</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Muadil marka</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Kod</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>50 ml fiyat (₺)</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>Kalıcılık (1-10)</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>Benzerlik (1-10)</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Ürün linki</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Cinsiyet</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Dior</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Sauvage</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Bargello</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>567</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E18" s="9" t="n">
         <v>600</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F18" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G18" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>https://marka-sitesi.com/urun/567</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Örnekler yalnızca biçimi göstermek içindir; bu sayfa yüklenmez.</t>
         </is>
